--- a/system_development/Damascus/V0.5/BOM-Damascus-V0.5.xlsx
+++ b/system_development/Damascus/V0.5/BOM-Damascus-V0.5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adowney2\Documents\GitHub\In-situ-monitoring-of-powder-bed-fusion-additive-manufacturing\system_development\Damascus\V0.5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\In-situ-monitoring-of-powder-bed-fusion-additive-manufacturing\system_development\Damascus\V0.5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B08A0FE1-72F4-417C-BC56-3C6611F1B985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3289B5DA-7DD4-4231-890D-9339195216B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-6540" windowWidth="16440" windowHeight="28320" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="28680" yWindow="-150" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
   <si>
     <t>Total Cost</t>
   </si>
@@ -245,9 +245,6 @@
     <t>2X3 SPOT LIGHT</t>
   </si>
   <si>
-    <t xml:space="preserve">eBay, need to find a local distirbutor </t>
-  </si>
-  <si>
     <t>Eathnet hub power sully</t>
   </si>
   <si>
@@ -270,6 +267,12 @@
   </si>
   <si>
     <t>https://www.newegg.com/trendnet-ti-bg50611/p/0XP-001A-009D1?Item=9SIAHFEKFX4055&amp;_gl=1*1sahfwo*_gcl_au*MTgzODUzMjA1Ni4xNzgyODczNzcy*_ga*OTMxODU5NDQwLjE3ODI4NzM3NzQ.*_ga_TR46GG8HLR*czE3ODI4NzcwNzAkbzIkZzEkdDE3ODI4NzcwNzMkajU3JGwwJGgxNDc0Njg5MTYy</t>
+  </si>
+  <si>
+    <t>CIMTEC Automation</t>
+  </si>
+  <si>
+    <t>Used off Ebay is a good source</t>
   </si>
 </sst>
 </file>
@@ -311,10 +314,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
       <color rgb="FF444444"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -347,7 +351,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -368,17 +372,25 @@
     <xf numFmtId="7" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="7" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -774,22 +786,22 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10">
         <v>1</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="11">
         <v>800</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="11">
         <f>D2*E2</f>
         <v>800</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="12" t="s">
         <v>14</v>
       </c>
       <c r="H2" s="1" t="s">
@@ -798,546 +810,550 @@
       <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="10">
         <v>6333220</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="10">
         <v>2</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="11">
         <v>12.7</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="11">
         <f>D3*E3</f>
         <v>25.4</v>
       </c>
-      <c r="G3" s="5"/>
+      <c r="G3" s="12"/>
       <c r="H3" s="1" t="s">
         <v>18</v>
       </c>
       <c r="I3" s="4"/>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="10">
         <v>1</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="11">
         <v>73.290000000000006</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="11">
         <f t="shared" ref="F4" si="0">D4*E4</f>
         <v>73.290000000000006</v>
       </c>
-      <c r="G4" s="5"/>
+      <c r="G4" s="12"/>
       <c r="H4" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10">
-        <f>D5*E5</f>
-        <v>0</v>
-      </c>
-      <c r="G5" s="5"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11">
+        <f t="shared" ref="F5:F28" si="1">D5*E5</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="12"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10">
-        <f>D6*E6</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="5"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="12"/>
       <c r="H6" s="1"/>
       <c r="I6" s="4"/>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10">
-        <f>D7*E7</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="5"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="12"/>
       <c r="H7" s="1"/>
       <c r="I7" s="4"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10">
-        <f>D8*E8</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="5"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="12"/>
       <c r="H8" s="1"/>
       <c r="I8" s="4"/>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10">
-        <f>D9*E9</f>
-        <v>0</v>
-      </c>
-      <c r="G9" s="5"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G9" s="12"/>
       <c r="H9" s="1"/>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10">
-        <f>D10*E10</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="5"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G10" s="12"/>
       <c r="H10" s="1"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="10">
         <v>1</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="11">
         <v>4.7</v>
       </c>
-      <c r="F11" s="10">
-        <f>D11*E11</f>
+      <c r="F11" s="11">
+        <f t="shared" si="1"/>
         <v>4.7</v>
       </c>
-      <c r="G11" s="5"/>
+      <c r="G11" s="12"/>
       <c r="H11" s="1" t="s">
         <v>45</v>
       </c>
       <c r="I11" s="3"/>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="10">
         <v>1</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="11">
         <v>7.58</v>
       </c>
-      <c r="F12" s="10">
-        <f>D12*E12</f>
+      <c r="F12" s="11">
+        <f t="shared" si="1"/>
         <v>7.58</v>
       </c>
-      <c r="G12" s="5"/>
+      <c r="G12" s="12"/>
       <c r="H12" s="1" t="s">
         <v>49</v>
       </c>
       <c r="I12" s="4"/>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="10">
         <v>1</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="11">
         <v>1.54</v>
       </c>
-      <c r="F13" s="10">
-        <f>D13*E13</f>
+      <c r="F13" s="11">
+        <f t="shared" si="1"/>
         <v>1.54</v>
       </c>
-      <c r="G13" s="5"/>
+      <c r="G13" s="12"/>
       <c r="H13" s="1" t="s">
         <v>55</v>
       </c>
       <c r="I13" s="4"/>
     </row>
     <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="10">
         <v>1</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="11">
         <v>2.95</v>
       </c>
-      <c r="F14" s="10">
-        <f>D14*E14</f>
+      <c r="F14" s="11">
+        <f t="shared" si="1"/>
         <v>2.95</v>
       </c>
-      <c r="G14" s="5"/>
+      <c r="G14" s="12"/>
       <c r="H14" s="1" t="s">
         <v>58</v>
       </c>
       <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10">
-        <f>D15*E15</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="5"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="12"/>
       <c r="H15" s="1"/>
       <c r="I15" s="4"/>
     </row>
     <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10">
-        <f>D16*E16</f>
-        <v>0</v>
-      </c>
-      <c r="G16" s="5"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="12"/>
       <c r="H16" s="1"/>
       <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10">
-        <f>D17*E17</f>
-        <v>0</v>
-      </c>
-      <c r="G17" s="5"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="12"/>
       <c r="H17" s="1"/>
       <c r="I17" s="4"/>
     </row>
     <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10">
-        <f>D18*E18</f>
-        <v>0</v>
-      </c>
-      <c r="G18" s="5"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G18" s="12"/>
       <c r="H18" s="1"/>
       <c r="I18" s="4"/>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10">
-        <f>D19*E19</f>
-        <v>0</v>
-      </c>
-      <c r="G19" s="5"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G19" s="12"/>
       <c r="H19" s="1"/>
       <c r="I19" s="4"/>
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10">
-        <f>D20*E20</f>
-        <v>0</v>
-      </c>
-      <c r="G20" s="5"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G20" s="12"/>
       <c r="H20" s="1"/>
       <c r="I20" s="4"/>
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10">
-        <f>D21*E21</f>
-        <v>0</v>
-      </c>
-      <c r="G21" s="5"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="12"/>
       <c r="H21" s="1"/>
       <c r="I21" s="4"/>
     </row>
     <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="10">
-        <f>D22*E22</f>
-        <v>0</v>
-      </c>
-      <c r="G22" s="5"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="12"/>
       <c r="H22" s="3"/>
       <c r="I22" s="4"/>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="10">
         <v>1</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="11">
         <v>110</v>
       </c>
-      <c r="F23" s="10">
-        <f>D23*E23</f>
+      <c r="F23" s="11">
+        <f t="shared" si="1"/>
         <v>110</v>
       </c>
-      <c r="G23" s="5"/>
+      <c r="G23" s="12"/>
       <c r="H23" s="3" t="s">
         <v>44</v>
       </c>
       <c r="I23" s="4"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="10">
         <v>2903361</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="10">
         <v>2</v>
       </c>
-      <c r="E24" s="10">
+      <c r="E24" s="11">
         <v>9.4600000000000009</v>
       </c>
-      <c r="F24" s="10">
-        <f>D24*E24</f>
+      <c r="F24" s="11">
+        <f t="shared" si="1"/>
         <v>18.920000000000002</v>
       </c>
-      <c r="G24" s="5"/>
+      <c r="G24" s="12"/>
       <c r="H24" s="3" t="s">
         <v>61</v>
       </c>
       <c r="I24" s="4"/>
     </row>
     <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="10">
         <v>1</v>
       </c>
-      <c r="E25" s="10">
+      <c r="E25" s="11">
         <v>13.96</v>
       </c>
-      <c r="F25" s="10">
-        <f>D25*E25</f>
+      <c r="F25" s="11">
+        <f t="shared" si="1"/>
         <v>13.96</v>
       </c>
-      <c r="G25" s="2"/>
+      <c r="G25" s="10"/>
       <c r="H25" s="1" t="s">
         <v>63</v>
       </c>
       <c r="I25" s="4"/>
     </row>
     <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="10">
         <v>2</v>
       </c>
-      <c r="E26" s="10">
-        <v>200</v>
-      </c>
-      <c r="F26" s="10">
-        <f>D26*E26</f>
-        <v>400</v>
-      </c>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2" t="s">
+      <c r="E26" s="11">
+        <v>695.33</v>
+      </c>
+      <c r="F26" s="11">
+        <f t="shared" si="1"/>
+        <v>1390.66</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H26" t="s">
+        <v>77</v>
+      </c>
+      <c r="I26" s="2"/>
+    </row>
+    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="10" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
+      <c r="B27" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="C27" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="D27" s="10">
+        <v>1</v>
+      </c>
+      <c r="E27" s="11">
+        <v>23</v>
+      </c>
+      <c r="F27" s="11">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="G27" s="10"/>
+      <c r="H27" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D27" s="2">
+    </row>
+    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D28" s="10">
         <v>1</v>
       </c>
-      <c r="E27" s="10">
-        <v>23</v>
-      </c>
-      <c r="F27" s="10">
-        <f>D27*E27</f>
-        <v>23</v>
-      </c>
-      <c r="G27" s="2"/>
-      <c r="H27" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C28" s="2" t="s">
+      <c r="E28" s="14">
+        <v>329</v>
+      </c>
+      <c r="F28" s="14">
+        <f t="shared" si="1"/>
+        <v>329</v>
+      </c>
+      <c r="G28" s="9"/>
+      <c r="H28" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="D28" s="2">
-        <v>1</v>
-      </c>
-      <c r="E28" s="11">
-        <v>329</v>
-      </c>
-      <c r="F28" s="11">
-        <f>D28*E28</f>
-        <v>329</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="36" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
     </row>
     <row r="37" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E37" s="7" t="s">
@@ -1345,7 +1361,7 @@
       </c>
       <c r="F37" s="5">
         <f>SUM(F2:F36)</f>
-        <v>1810.3400000000001</v>
+        <v>2801</v>
       </c>
     </row>
   </sheetData>

--- a/system_development/Damascus/V0.5/BOM-Damascus-V0.5.xlsx
+++ b/system_development/Damascus/V0.5/BOM-Damascus-V0.5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\In-situ-monitoring-of-powder-bed-fusion-additive-manufacturing\system_development\Damascus\V0.5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3289B5DA-7DD4-4231-890D-9339195216B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D886170-94FA-42FC-AB7F-4BAC53439378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-150" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
   <si>
     <t>Total Cost</t>
   </si>
@@ -273,6 +273,54 @@
   </si>
   <si>
     <t>Used off Ebay is a good source</t>
+  </si>
+  <si>
+    <t>switch to thunderbold patch cable</t>
+  </si>
+  <si>
+    <t>10 GBE to Thunderbolt adapter</t>
+  </si>
+  <si>
+    <t>Eaton Tripp Lite Series Cat6a 10G Snagless Shielded STP Ethernet Cable (RJ45 M/M), PoE, Blue, 1 ft. (0.31 m) - patch</t>
+  </si>
+  <si>
+    <t>N262-001-BL</t>
+  </si>
+  <si>
+    <t>OWC 1.0M (39.4") Thunderbolt 5 (USB-C) Cable Black for Thunderbolt And USB-C Devices - Black</t>
+  </si>
+  <si>
+    <t>1M Thunderbolt cable</t>
+  </si>
+  <si>
+    <t>OWC 2.0M (78") Thunderbolt 4 (USB-C) Cable for Thunderbolt And USB-C Devices - Black</t>
+  </si>
+  <si>
+    <t>2M Thunderbolt cable</t>
+  </si>
+  <si>
+    <t>OWCCBLTB4C2.0M</t>
+  </si>
+  <si>
+    <t>OWCCBLTB5C1.0M</t>
+  </si>
+  <si>
+    <t>OWC Thunderbolt 4 10G Ethernet Adapter</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OWCTB4ADP10GBE</t>
+  </si>
+  <si>
+    <t>https://www.cdwg.com/product/owc-thunderbolt-4-10g-ethernet-adapter/8482162</t>
+  </si>
+  <si>
+    <t>https://www.cdwg.com/product/owc-1.0m-39.4-thunderbolt-5-usb-c-cable-black-for-thunderbolt-and-usb/8269345</t>
+  </si>
+  <si>
+    <t>https://www.cdwg.com/product/owc-2.0m-78-thunderbolt-4-usb-c-cable-for-thunderbolt-and-usb-c-device/7390529</t>
+  </si>
+  <si>
+    <t>https://www.cdwg.com/product/tripp-lite-1ft-augmented-cat6a-shielded-stp-snagless-patch-cable-blue-1ft/3726348</t>
   </si>
 </sst>
 </file>
@@ -283,7 +331,7 @@
     <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -320,6 +368,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF150404"/>
+      <name val="Source Sans Pro"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -351,7 +405,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -373,24 +427,17 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="7" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -786,22 +833,22 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2">
         <v>1</v>
       </c>
-      <c r="E2" s="11">
+      <c r="E2" s="9">
         <v>800</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="9">
         <f>D2*E2</f>
         <v>800</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H2" s="1" t="s">
@@ -810,487 +857,487 @@
       <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="2">
         <v>6333220</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="2">
         <v>2</v>
       </c>
-      <c r="E3" s="11">
+      <c r="E3" s="9">
         <v>12.7</v>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="9">
         <f>D3*E3</f>
         <v>25.4</v>
       </c>
-      <c r="G3" s="12"/>
+      <c r="G3" s="5"/>
       <c r="H3" s="1" t="s">
         <v>18</v>
       </c>
       <c r="I3" s="4"/>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="2">
         <v>1</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="9">
         <v>73.290000000000006</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="9">
         <f t="shared" ref="F4" si="0">D4*E4</f>
         <v>73.290000000000006</v>
       </c>
-      <c r="G4" s="12"/>
+      <c r="G4" s="5"/>
       <c r="H4" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11">
-        <f t="shared" ref="F5:F28" si="1">D5*E5</f>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9">
+        <f t="shared" ref="F5:F32" si="1">D5*E5</f>
         <v>0</v>
       </c>
-      <c r="G5" s="12"/>
+      <c r="G5" s="5"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G6" s="12"/>
+      <c r="G6" s="5"/>
       <c r="H6" s="1"/>
       <c r="I6" s="4"/>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11">
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G7" s="12"/>
+      <c r="G7" s="5"/>
       <c r="H7" s="1"/>
       <c r="I7" s="4"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11">
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G8" s="12"/>
+      <c r="G8" s="5"/>
       <c r="H8" s="1"/>
       <c r="I8" s="4"/>
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11">
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G9" s="12"/>
+      <c r="G9" s="5"/>
       <c r="H9" s="1"/>
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11">
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G10" s="12"/>
+      <c r="G10" s="5"/>
       <c r="H10" s="1"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="2">
         <v>1</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="9">
         <v>4.7</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="9">
         <f t="shared" si="1"/>
         <v>4.7</v>
       </c>
-      <c r="G11" s="12"/>
+      <c r="G11" s="5"/>
       <c r="H11" s="1" t="s">
         <v>45</v>
       </c>
       <c r="I11" s="3"/>
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="2">
         <v>1</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="9">
         <v>7.58</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="9">
         <f t="shared" si="1"/>
         <v>7.58</v>
       </c>
-      <c r="G12" s="12"/>
+      <c r="G12" s="5"/>
       <c r="H12" s="1" t="s">
         <v>49</v>
       </c>
       <c r="I12" s="4"/>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="2">
         <v>1</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="9">
         <v>1.54</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="9">
         <f t="shared" si="1"/>
         <v>1.54</v>
       </c>
-      <c r="G13" s="12"/>
+      <c r="G13" s="5"/>
       <c r="H13" s="1" t="s">
         <v>55</v>
       </c>
       <c r="I13" s="4"/>
     </row>
     <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="2">
         <v>1</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="9">
         <v>2.95</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="9">
         <f t="shared" si="1"/>
         <v>2.95</v>
       </c>
-      <c r="G14" s="12"/>
+      <c r="G14" s="5"/>
       <c r="H14" s="1" t="s">
         <v>58</v>
       </c>
       <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11">
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G15" s="12"/>
+      <c r="G15" s="5"/>
       <c r="H15" s="1"/>
       <c r="I15" s="4"/>
     </row>
     <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11">
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G16" s="12"/>
+      <c r="G16" s="5"/>
       <c r="H16" s="1"/>
       <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11">
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G17" s="12"/>
+      <c r="G17" s="5"/>
       <c r="H17" s="1"/>
       <c r="I17" s="4"/>
     </row>
     <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11">
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G18" s="12"/>
+      <c r="G18" s="5"/>
       <c r="H18" s="1"/>
       <c r="I18" s="4"/>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G19" s="12"/>
+      <c r="G19" s="5"/>
       <c r="H19" s="1"/>
       <c r="I19" s="4"/>
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11">
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G20" s="12"/>
+      <c r="G20" s="5"/>
       <c r="H20" s="1"/>
       <c r="I20" s="4"/>
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11">
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G21" s="12"/>
+      <c r="G21" s="5"/>
       <c r="H21" s="1"/>
       <c r="I21" s="4"/>
     </row>
     <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="11">
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G22" s="12"/>
+      <c r="G22" s="5"/>
       <c r="H22" s="3"/>
       <c r="I22" s="4"/>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="D23" s="10">
+      <c r="D23" s="2">
         <v>1</v>
       </c>
-      <c r="E23" s="11">
+      <c r="E23" s="9">
         <v>110</v>
       </c>
-      <c r="F23" s="11">
+      <c r="F23" s="9">
         <f t="shared" si="1"/>
         <v>110</v>
       </c>
-      <c r="G23" s="12"/>
+      <c r="G23" s="5"/>
       <c r="H23" s="3" t="s">
         <v>44</v>
       </c>
       <c r="I23" s="4"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="10">
+      <c r="C24" s="2">
         <v>2903361</v>
       </c>
-      <c r="D24" s="10">
+      <c r="D24" s="2">
         <v>2</v>
       </c>
-      <c r="E24" s="11">
+      <c r="E24" s="9">
         <v>9.4600000000000009</v>
       </c>
-      <c r="F24" s="11">
+      <c r="F24" s="9">
         <f t="shared" si="1"/>
         <v>18.920000000000002</v>
       </c>
-      <c r="G24" s="12"/>
+      <c r="G24" s="5"/>
       <c r="H24" s="3" t="s">
         <v>61</v>
       </c>
       <c r="I24" s="4"/>
     </row>
     <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D25" s="10">
+      <c r="D25" s="2">
         <v>1</v>
       </c>
-      <c r="E25" s="11">
+      <c r="E25" s="9">
         <v>13.96</v>
       </c>
-      <c r="F25" s="11">
+      <c r="F25" s="9">
         <f t="shared" si="1"/>
         <v>13.96</v>
       </c>
-      <c r="G25" s="10"/>
+      <c r="G25" s="2"/>
       <c r="H25" s="1" t="s">
         <v>63</v>
       </c>
       <c r="I25" s="4"/>
     </row>
     <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D26" s="10">
+      <c r="D26" s="2">
         <v>2</v>
       </c>
-      <c r="E26" s="11">
+      <c r="E26" s="9">
         <v>695.33</v>
       </c>
-      <c r="F26" s="11">
+      <c r="F26" s="9">
         <f t="shared" si="1"/>
         <v>1390.66</v>
       </c>
-      <c r="G26" s="10" t="s">
+      <c r="G26" s="2" t="s">
         <v>78</v>
       </c>
       <c r="H26" t="s">
@@ -1299,58 +1346,150 @@
       <c r="I26" s="2"/>
     </row>
     <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="10" t="s">
+      <c r="A27" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="D27" s="10">
+      <c r="D27" s="2">
         <v>1</v>
       </c>
-      <c r="E27" s="11">
+      <c r="E27" s="9">
         <v>23</v>
       </c>
-      <c r="F27" s="11">
+      <c r="F27" s="9">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="G27" s="10"/>
+      <c r="G27" s="2"/>
       <c r="H27" s="1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
+      <c r="A28" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D28" s="10">
+      <c r="D28" s="2">
         <v>1</v>
       </c>
-      <c r="E28" s="14">
+      <c r="E28" s="8">
         <v>329</v>
       </c>
-      <c r="F28" s="14">
+      <c r="F28" s="8">
         <f t="shared" si="1"/>
         <v>329</v>
       </c>
-      <c r="G28" s="9"/>
       <c r="H28" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D29" s="2">
+        <v>1</v>
+      </c>
+      <c r="E29" s="9">
+        <v>7.62</v>
+      </c>
+      <c r="F29" s="9">
+        <f t="shared" si="1"/>
+        <v>7.62</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D30" s="2">
+        <v>1</v>
+      </c>
+      <c r="E30" s="9">
+        <v>181.53</v>
+      </c>
+      <c r="F30" s="9">
+        <f t="shared" si="1"/>
+        <v>181.53</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C31" t="s">
+        <v>87</v>
+      </c>
+      <c r="D31" s="2">
+        <v>1</v>
+      </c>
+      <c r="E31" s="9">
+        <v>49.29</v>
+      </c>
+      <c r="F31" s="9">
+        <f t="shared" si="1"/>
+        <v>49.29</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" t="s">
+        <v>88</v>
+      </c>
+      <c r="D32" s="2">
+        <v>1</v>
+      </c>
+      <c r="E32" s="9">
+        <v>30.51</v>
+      </c>
+      <c r="F32" s="9">
+        <f t="shared" si="1"/>
+        <v>30.51</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
     <row r="36" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E36" s="8"/>
       <c r="F36" s="8"/>
@@ -1361,7 +1500,7 @@
       </c>
       <c r="F37" s="5">
         <f>SUM(F2:F36)</f>
-        <v>2801</v>
+        <v>3069.9500000000003</v>
       </c>
     </row>
   </sheetData>
@@ -1379,8 +1518,12 @@
     <hyperlink ref="H25" r:id="rId10" display="https://www.cdwg.com/product/tripp-lite-usb-3.0-adapter-converter-usb-a-to-usb-type-c-m-f-usb-c/5238658?pfm=srh" xr:uid="{3D280BFA-933C-4B78-9942-E3BEECE50362}"/>
     <hyperlink ref="H27" r:id="rId11" xr:uid="{69858AD3-97BB-4924-83ED-505EBD3B921C}"/>
     <hyperlink ref="H28" r:id="rId12" xr:uid="{E7CDAEAF-246E-429F-942C-8F1434B33468}"/>
+    <hyperlink ref="H30" r:id="rId13" xr:uid="{801BAFE3-F6D0-4BC5-8B21-256CC97C2787}"/>
+    <hyperlink ref="H32" r:id="rId14" xr:uid="{48EA4B1F-CBAD-4590-9666-2342E248E6D7}"/>
+    <hyperlink ref="H31" r:id="rId15" xr:uid="{009BE108-4464-476B-A6EC-083EA45298AB}"/>
+    <hyperlink ref="H29" r:id="rId16" xr:uid="{7AD70C87-5E84-47F4-BFB8-F408B6CD48AB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId13"/>
+  <pageSetup orientation="portrait" r:id="rId17"/>
 </worksheet>
 </file>